--- a/docs/Rivenlight_설정값_정리.xlsx
+++ b/docs/Rivenlight_설정값_정리.xlsx
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>방어력 DefenseMult</t>
+          <t>받는 데미지 배수 DefenseMult (방어력 감소)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3 (받는 피해 1.3배)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>로그 확인 완료</t>
+          <t>TakeDamage에서 데미지에 곱함 [노드 미확인]. 로그로 1.3 확인 완료</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
